--- a/examples/assets/sample.xlsx
+++ b/examples/assets/sample.xlsx
@@ -8,7 +8,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>2024 年水果銷售統計表</t>
+  </si>
   <si>
     <t>產品</t>
   </si>
@@ -41,37 +44,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>35</v>
-      </c>
-      <c r="D2">
-        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -79,13 +76,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D3">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
@@ -93,13 +90,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5">
@@ -107,13 +104,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>480</v>
+        <v>375</v>
       </c>
     </row>
     <row r="6">
@@ -121,12 +118,29 @@
         <v>8</v>
       </c>
       <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>60</v>
+      </c>
+      <c r="D6">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>53</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>1565</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
 </worksheet>
 </file>
--- a/examples/assets/sample.xlsx
+++ b/examples/assets/sample.xlsx
@@ -42,6 +42,93 @@
 </sst>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="3">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:D7"/>
@@ -49,93 +136,93 @@
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="3">
         <v>35</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>350</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>20</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>18</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>360</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>25</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>375</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="3">
+        <v>88</v>
+      </c>
+      <c r="C6" s="3">
         <v>60</v>
       </c>
-      <c r="D6">
-        <v>480</v>
+      <c r="D6" s="4">
+        <v>5280</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>53</v>
-      </c>
-      <c r="D7">
-        <v>1565</v>
+      <c r="B7" s="6">
+        <v>133</v>
+      </c>
+      <c r="D7" s="7">
+        <v>6365</v>
       </c>
     </row>
   </sheetData>

--- a/examples/assets/sample.xlsx
+++ b/examples/assets/sample.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="銷售表" sheetId="1" r:id="rId1"/>
+    <sheet name="明細" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>2024 年水果銷售統計表</t>
   </si>
@@ -38,6 +39,372 @@
   </si>
   <si>
     <t>合計</t>
+  </si>
+  <si>
+    <t>編號</t>
+  </si>
+  <si>
+    <t>品項</t>
+  </si>
+  <si>
+    <t>香蕉 批次 1</t>
+  </si>
+  <si>
+    <t>橘子 批次 2</t>
+  </si>
+  <si>
+    <t>葡萄 批次 3</t>
+  </si>
+  <si>
+    <t>西瓜 批次 4</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 5</t>
+  </si>
+  <si>
+    <t>芒果 批次 6</t>
+  </si>
+  <si>
+    <t>草莓 批次 7</t>
+  </si>
+  <si>
+    <t>蘋果 批次 8</t>
+  </si>
+  <si>
+    <t>香蕉 批次 9</t>
+  </si>
+  <si>
+    <t>橘子 批次 10</t>
+  </si>
+  <si>
+    <t>葡萄 批次 11</t>
+  </si>
+  <si>
+    <t>西瓜 批次 12</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 13</t>
+  </si>
+  <si>
+    <t>芒果 批次 14</t>
+  </si>
+  <si>
+    <t>草莓 批次 15</t>
+  </si>
+  <si>
+    <t>蘋果 批次 16</t>
+  </si>
+  <si>
+    <t>香蕉 批次 17</t>
+  </si>
+  <si>
+    <t>橘子 批次 18</t>
+  </si>
+  <si>
+    <t>葡萄 批次 19</t>
+  </si>
+  <si>
+    <t>西瓜 批次 20</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 21</t>
+  </si>
+  <si>
+    <t>芒果 批次 22</t>
+  </si>
+  <si>
+    <t>草莓 批次 23</t>
+  </si>
+  <si>
+    <t>蘋果 批次 24</t>
+  </si>
+  <si>
+    <t>香蕉 批次 25</t>
+  </si>
+  <si>
+    <t>橘子 批次 26</t>
+  </si>
+  <si>
+    <t>葡萄 批次 27</t>
+  </si>
+  <si>
+    <t>西瓜 批次 28</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 29</t>
+  </si>
+  <si>
+    <t>芒果 批次 30</t>
+  </si>
+  <si>
+    <t>草莓 批次 31</t>
+  </si>
+  <si>
+    <t>蘋果 批次 32</t>
+  </si>
+  <si>
+    <t>香蕉 批次 33</t>
+  </si>
+  <si>
+    <t>橘子 批次 34</t>
+  </si>
+  <si>
+    <t>葡萄 批次 35</t>
+  </si>
+  <si>
+    <t>西瓜 批次 36</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 37</t>
+  </si>
+  <si>
+    <t>芒果 批次 38</t>
+  </si>
+  <si>
+    <t>草莓 批次 39</t>
+  </si>
+  <si>
+    <t>蘋果 批次 40</t>
+  </si>
+  <si>
+    <t>香蕉 批次 41</t>
+  </si>
+  <si>
+    <t>橘子 批次 42</t>
+  </si>
+  <si>
+    <t>葡萄 批次 43</t>
+  </si>
+  <si>
+    <t>西瓜 批次 44</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 45</t>
+  </si>
+  <si>
+    <t>芒果 批次 46</t>
+  </si>
+  <si>
+    <t>草莓 批次 47</t>
+  </si>
+  <si>
+    <t>蘋果 批次 48</t>
+  </si>
+  <si>
+    <t>香蕉 批次 49</t>
+  </si>
+  <si>
+    <t>橘子 批次 50</t>
+  </si>
+  <si>
+    <t>葡萄 批次 51</t>
+  </si>
+  <si>
+    <t>西瓜 批次 52</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 53</t>
+  </si>
+  <si>
+    <t>芒果 批次 54</t>
+  </si>
+  <si>
+    <t>草莓 批次 55</t>
+  </si>
+  <si>
+    <t>蘋果 批次 56</t>
+  </si>
+  <si>
+    <t>香蕉 批次 57</t>
+  </si>
+  <si>
+    <t>橘子 批次 58</t>
+  </si>
+  <si>
+    <t>葡萄 批次 59</t>
+  </si>
+  <si>
+    <t>西瓜 批次 60</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 61</t>
+  </si>
+  <si>
+    <t>芒果 批次 62</t>
+  </si>
+  <si>
+    <t>草莓 批次 63</t>
+  </si>
+  <si>
+    <t>蘋果 批次 64</t>
+  </si>
+  <si>
+    <t>香蕉 批次 65</t>
+  </si>
+  <si>
+    <t>橘子 批次 66</t>
+  </si>
+  <si>
+    <t>葡萄 批次 67</t>
+  </si>
+  <si>
+    <t>西瓜 批次 68</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 69</t>
+  </si>
+  <si>
+    <t>芒果 批次 70</t>
+  </si>
+  <si>
+    <t>草莓 批次 71</t>
+  </si>
+  <si>
+    <t>蘋果 批次 72</t>
+  </si>
+  <si>
+    <t>香蕉 批次 73</t>
+  </si>
+  <si>
+    <t>橘子 批次 74</t>
+  </si>
+  <si>
+    <t>葡萄 批次 75</t>
+  </si>
+  <si>
+    <t>西瓜 批次 76</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 77</t>
+  </si>
+  <si>
+    <t>芒果 批次 78</t>
+  </si>
+  <si>
+    <t>草莓 批次 79</t>
+  </si>
+  <si>
+    <t>蘋果 批次 80</t>
+  </si>
+  <si>
+    <t>香蕉 批次 81</t>
+  </si>
+  <si>
+    <t>橘子 批次 82</t>
+  </si>
+  <si>
+    <t>葡萄 批次 83</t>
+  </si>
+  <si>
+    <t>西瓜 批次 84</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 85</t>
+  </si>
+  <si>
+    <t>芒果 批次 86</t>
+  </si>
+  <si>
+    <t>草莓 批次 87</t>
+  </si>
+  <si>
+    <t>蘋果 批次 88</t>
+  </si>
+  <si>
+    <t>香蕉 批次 89</t>
+  </si>
+  <si>
+    <t>橘子 批次 90</t>
+  </si>
+  <si>
+    <t>葡萄 批次 91</t>
+  </si>
+  <si>
+    <t>西瓜 批次 92</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 93</t>
+  </si>
+  <si>
+    <t>芒果 批次 94</t>
+  </si>
+  <si>
+    <t>草莓 批次 95</t>
+  </si>
+  <si>
+    <t>蘋果 批次 96</t>
+  </si>
+  <si>
+    <t>香蕉 批次 97</t>
+  </si>
+  <si>
+    <t>橘子 批次 98</t>
+  </si>
+  <si>
+    <t>葡萄 批次 99</t>
+  </si>
+  <si>
+    <t>西瓜 批次 100</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 101</t>
+  </si>
+  <si>
+    <t>芒果 批次 102</t>
+  </si>
+  <si>
+    <t>草莓 批次 103</t>
+  </si>
+  <si>
+    <t>蘋果 批次 104</t>
+  </si>
+  <si>
+    <t>香蕉 批次 105</t>
+  </si>
+  <si>
+    <t>橘子 批次 106</t>
+  </si>
+  <si>
+    <t>葡萄 批次 107</t>
+  </si>
+  <si>
+    <t>西瓜 批次 108</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 109</t>
+  </si>
+  <si>
+    <t>芒果 批次 110</t>
+  </si>
+  <si>
+    <t>草莓 批次 111</t>
+  </si>
+  <si>
+    <t>蘋果 批次 112</t>
+  </si>
+  <si>
+    <t>香蕉 批次 113</t>
+  </si>
+  <si>
+    <t>橘子 批次 114</t>
+  </si>
+  <si>
+    <t>葡萄 批次 115</t>
+  </si>
+  <si>
+    <t>西瓜 批次 116</t>
+  </si>
+  <si>
+    <t>鳳梨 批次 117</t>
+  </si>
+  <si>
+    <t>芒果 批次 118</t>
+  </si>
+  <si>
+    <t>草莓 批次 119</t>
+  </si>
+  <si>
+    <t>蘋果 批次 120</t>
   </si>
 </sst>
 </file>
@@ -230,4 +597,2076 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E121"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7</v>
+      </c>
+      <c r="D3" s="4">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4">
+        <v>38</v>
+      </c>
+      <c r="E5" s="4">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4">
+        <v>45</v>
+      </c>
+      <c r="E6" s="4">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3">
+        <v>22</v>
+      </c>
+      <c r="D8" s="4">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3">
+        <v>25</v>
+      </c>
+      <c r="D9" s="4">
+        <v>66</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3">
+        <v>28</v>
+      </c>
+      <c r="D10" s="4">
+        <v>73</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="3">
+        <v>31</v>
+      </c>
+      <c r="D11" s="4">
+        <v>80</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4">
+        <v>87</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2958</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="3">
+        <v>37</v>
+      </c>
+      <c r="D13" s="4">
+        <v>14</v>
+      </c>
+      <c r="E13" s="4">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="3">
+        <v>40</v>
+      </c>
+      <c r="D14" s="4">
+        <v>21</v>
+      </c>
+      <c r="E14" s="4">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="3">
+        <v>43</v>
+      </c>
+      <c r="D15" s="4">
+        <v>28</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46</v>
+      </c>
+      <c r="D16" s="4">
+        <v>35</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="3">
+        <v>49</v>
+      </c>
+      <c r="D17" s="4">
+        <v>42</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3">
+        <v>52</v>
+      </c>
+      <c r="D18" s="4">
+        <v>49</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="3">
+        <v>55</v>
+      </c>
+      <c r="D19" s="4">
+        <v>56</v>
+      </c>
+      <c r="E19" s="4">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3">
+        <v>58</v>
+      </c>
+      <c r="D20" s="4">
+        <v>63</v>
+      </c>
+      <c r="E20" s="4">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="3">
+        <v>61</v>
+      </c>
+      <c r="D21" s="4">
+        <v>70</v>
+      </c>
+      <c r="E21" s="4">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="3">
+        <v>64</v>
+      </c>
+      <c r="D22" s="4">
+        <v>77</v>
+      </c>
+      <c r="E22" s="4">
+        <v>4928</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3">
+        <v>67</v>
+      </c>
+      <c r="D23" s="4">
+        <v>84</v>
+      </c>
+      <c r="E23" s="4">
+        <v>5628</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="3">
+        <v>70</v>
+      </c>
+      <c r="D24" s="4">
+        <v>11</v>
+      </c>
+      <c r="E24" s="4">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="3">
+        <v>73</v>
+      </c>
+      <c r="D25" s="4">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="3">
+        <v>76</v>
+      </c>
+      <c r="D26" s="4">
+        <v>25</v>
+      </c>
+      <c r="E26" s="4">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="3">
+        <v>79</v>
+      </c>
+      <c r="D27" s="4">
+        <v>32</v>
+      </c>
+      <c r="E27" s="4">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="3">
+        <v>82</v>
+      </c>
+      <c r="D28" s="4">
+        <v>39</v>
+      </c>
+      <c r="E28" s="4">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="3">
+        <v>85</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46</v>
+      </c>
+      <c r="E29" s="4">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3">
+        <v>88</v>
+      </c>
+      <c r="D30" s="4">
+        <v>53</v>
+      </c>
+      <c r="E30" s="4">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4">
+        <v>60</v>
+      </c>
+      <c r="E31" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="3">
+        <v>4</v>
+      </c>
+      <c r="D32" s="4">
+        <v>67</v>
+      </c>
+      <c r="E32" s="4">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="3">
+        <v>7</v>
+      </c>
+      <c r="D33" s="4">
+        <v>74</v>
+      </c>
+      <c r="E33" s="4">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="3">
+        <v>10</v>
+      </c>
+      <c r="D34" s="4">
+        <v>81</v>
+      </c>
+      <c r="E34" s="4">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="3">
+        <v>13</v>
+      </c>
+      <c r="D35" s="4">
+        <v>88</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="3">
+        <v>16</v>
+      </c>
+      <c r="D36" s="4">
+        <v>15</v>
+      </c>
+      <c r="E36" s="4">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="3">
+        <v>19</v>
+      </c>
+      <c r="D37" s="4">
+        <v>22</v>
+      </c>
+      <c r="E37" s="4">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="3">
+        <v>22</v>
+      </c>
+      <c r="D38" s="4">
+        <v>29</v>
+      </c>
+      <c r="E38" s="4">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="3">
+        <v>25</v>
+      </c>
+      <c r="D39" s="4">
+        <v>36</v>
+      </c>
+      <c r="E39" s="4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="3">
+        <v>28</v>
+      </c>
+      <c r="D40" s="4">
+        <v>43</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="3">
+        <v>31</v>
+      </c>
+      <c r="D41" s="4">
+        <v>50</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="3">
+        <v>34</v>
+      </c>
+      <c r="D42" s="4">
+        <v>57</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="3">
+        <v>37</v>
+      </c>
+      <c r="D43" s="4">
+        <v>64</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="3">
+        <v>40</v>
+      </c>
+      <c r="D44" s="4">
+        <v>71</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="3">
+        <v>43</v>
+      </c>
+      <c r="D45" s="4">
+        <v>78</v>
+      </c>
+      <c r="E45" s="4">
+        <v>3354</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="3">
+        <v>46</v>
+      </c>
+      <c r="D46" s="4">
+        <v>85</v>
+      </c>
+      <c r="E46" s="4">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="3">
+        <v>49</v>
+      </c>
+      <c r="D47" s="4">
+        <v>12</v>
+      </c>
+      <c r="E47" s="4">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="3">
+        <v>52</v>
+      </c>
+      <c r="D48" s="4">
+        <v>19</v>
+      </c>
+      <c r="E48" s="4">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="3">
+        <v>55</v>
+      </c>
+      <c r="D49" s="4">
+        <v>26</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="3">
+        <v>58</v>
+      </c>
+      <c r="D50" s="4">
+        <v>33</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="3">
+        <v>61</v>
+      </c>
+      <c r="D51" s="4">
+        <v>40</v>
+      </c>
+      <c r="E51" s="4">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="3">
+        <v>64</v>
+      </c>
+      <c r="D52" s="4">
+        <v>47</v>
+      </c>
+      <c r="E52" s="4">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="3">
+        <v>67</v>
+      </c>
+      <c r="D53" s="4">
+        <v>54</v>
+      </c>
+      <c r="E53" s="4">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C54" s="3">
+        <v>70</v>
+      </c>
+      <c r="D54" s="4">
+        <v>61</v>
+      </c>
+      <c r="E54" s="4">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="3">
+        <v>73</v>
+      </c>
+      <c r="D55" s="4">
+        <v>68</v>
+      </c>
+      <c r="E55" s="4">
+        <v>4964</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="3">
+        <v>76</v>
+      </c>
+      <c r="D56" s="4">
+        <v>75</v>
+      </c>
+      <c r="E56" s="4">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="3">
+        <v>79</v>
+      </c>
+      <c r="D57" s="4">
+        <v>82</v>
+      </c>
+      <c r="E57" s="4">
+        <v>6478</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="3">
+        <v>82</v>
+      </c>
+      <c r="D58" s="4">
+        <v>89</v>
+      </c>
+      <c r="E58" s="4">
+        <v>7298</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="3">
+        <v>85</v>
+      </c>
+      <c r="D59" s="4">
+        <v>16</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3">
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="3">
+        <v>88</v>
+      </c>
+      <c r="D60" s="4">
+        <v>23</v>
+      </c>
+      <c r="E60" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+      <c r="D61" s="4">
+        <v>30</v>
+      </c>
+      <c r="E61" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="3">
+        <v>4</v>
+      </c>
+      <c r="D62" s="4">
+        <v>37</v>
+      </c>
+      <c r="E62" s="4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="3">
+        <v>7</v>
+      </c>
+      <c r="D63" s="4">
+        <v>44</v>
+      </c>
+      <c r="E63" s="4">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="3">
+        <v>10</v>
+      </c>
+      <c r="D64" s="4">
+        <v>51</v>
+      </c>
+      <c r="E64" s="4">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" s="3">
+        <v>13</v>
+      </c>
+      <c r="D65" s="4">
+        <v>58</v>
+      </c>
+      <c r="E65" s="4">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="3">
+        <v>16</v>
+      </c>
+      <c r="D66" s="4">
+        <v>65</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="3">
+        <v>19</v>
+      </c>
+      <c r="D67" s="4">
+        <v>72</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="3">
+        <v>22</v>
+      </c>
+      <c r="D68" s="4">
+        <v>79</v>
+      </c>
+      <c r="E68" s="4">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69" s="3">
+        <v>25</v>
+      </c>
+      <c r="D69" s="4">
+        <v>86</v>
+      </c>
+      <c r="E69" s="4">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="3">
+        <v>28</v>
+      </c>
+      <c r="D70" s="4">
+        <v>13</v>
+      </c>
+      <c r="E70" s="4">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="3">
+        <v>31</v>
+      </c>
+      <c r="D71" s="4">
+        <v>20</v>
+      </c>
+      <c r="E71" s="4">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C72" s="3">
+        <v>34</v>
+      </c>
+      <c r="D72" s="4">
+        <v>27</v>
+      </c>
+      <c r="E72" s="4">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="3">
+        <v>37</v>
+      </c>
+      <c r="D73" s="4">
+        <v>34</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" s="3">
+        <v>40</v>
+      </c>
+      <c r="D74" s="4">
+        <v>41</v>
+      </c>
+      <c r="E74" s="4">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C75" s="3">
+        <v>43</v>
+      </c>
+      <c r="D75" s="4">
+        <v>48</v>
+      </c>
+      <c r="E75" s="4">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="3">
+        <v>46</v>
+      </c>
+      <c r="D76" s="4">
+        <v>55</v>
+      </c>
+      <c r="E76" s="4">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C77" s="3">
+        <v>49</v>
+      </c>
+      <c r="D77" s="4">
+        <v>62</v>
+      </c>
+      <c r="E77" s="4">
+        <v>3038</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="3">
+        <v>52</v>
+      </c>
+      <c r="D78" s="4">
+        <v>69</v>
+      </c>
+      <c r="E78" s="4">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="3">
+        <v>55</v>
+      </c>
+      <c r="D79" s="4">
+        <v>76</v>
+      </c>
+      <c r="E79" s="4">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" s="3">
+        <v>58</v>
+      </c>
+      <c r="D80" s="4">
+        <v>83</v>
+      </c>
+      <c r="E80" s="4">
+        <v>4814</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="3">
+        <v>61</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10</v>
+      </c>
+      <c r="E81" s="4">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" s="3">
+        <v>64</v>
+      </c>
+      <c r="D82" s="4">
+        <v>17</v>
+      </c>
+      <c r="E82" s="4">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="3">
+        <v>67</v>
+      </c>
+      <c r="D83" s="4">
+        <v>24</v>
+      </c>
+      <c r="E83" s="4">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3">
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="3">
+        <v>70</v>
+      </c>
+      <c r="D84" s="4">
+        <v>31</v>
+      </c>
+      <c r="E84" s="4">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3">
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="3">
+        <v>73</v>
+      </c>
+      <c r="D85" s="4">
+        <v>38</v>
+      </c>
+      <c r="E85" s="4">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3">
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="3">
+        <v>76</v>
+      </c>
+      <c r="D86" s="4">
+        <v>45</v>
+      </c>
+      <c r="E86" s="4">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" s="3">
+        <v>79</v>
+      </c>
+      <c r="D87" s="4">
+        <v>52</v>
+      </c>
+      <c r="E87" s="4">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" s="3">
+        <v>82</v>
+      </c>
+      <c r="D88" s="4">
+        <v>59</v>
+      </c>
+      <c r="E88" s="4">
+        <v>4838</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="3">
+        <v>85</v>
+      </c>
+      <c r="D89" s="4">
+        <v>66</v>
+      </c>
+      <c r="E89" s="4">
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="3">
+        <v>88</v>
+      </c>
+      <c r="D90" s="4">
+        <v>73</v>
+      </c>
+      <c r="E90" s="4">
+        <v>6424</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="4">
+        <v>80</v>
+      </c>
+      <c r="E91" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="3">
+        <v>4</v>
+      </c>
+      <c r="D92" s="4">
+        <v>87</v>
+      </c>
+      <c r="E92" s="4">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="3">
+        <v>7</v>
+      </c>
+      <c r="D93" s="4">
+        <v>14</v>
+      </c>
+      <c r="E93" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="3">
+        <v>10</v>
+      </c>
+      <c r="D94" s="4">
+        <v>21</v>
+      </c>
+      <c r="E94" s="4">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3">
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95" s="3">
+        <v>13</v>
+      </c>
+      <c r="D95" s="4">
+        <v>28</v>
+      </c>
+      <c r="E95" s="4">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3">
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="3">
+        <v>16</v>
+      </c>
+      <c r="D96" s="4">
+        <v>35</v>
+      </c>
+      <c r="E96" s="4">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3">
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="3">
+        <v>19</v>
+      </c>
+      <c r="D97" s="4">
+        <v>42</v>
+      </c>
+      <c r="E97" s="4">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3">
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="3">
+        <v>22</v>
+      </c>
+      <c r="D98" s="4">
+        <v>49</v>
+      </c>
+      <c r="E98" s="4">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3">
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C99" s="3">
+        <v>25</v>
+      </c>
+      <c r="D99" s="4">
+        <v>56</v>
+      </c>
+      <c r="E99" s="4">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3">
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="3">
+        <v>28</v>
+      </c>
+      <c r="D100" s="4">
+        <v>63</v>
+      </c>
+      <c r="E100" s="4">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3">
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" s="3">
+        <v>31</v>
+      </c>
+      <c r="D101" s="4">
+        <v>70</v>
+      </c>
+      <c r="E101" s="4">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3">
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="3">
+        <v>34</v>
+      </c>
+      <c r="D102" s="4">
+        <v>77</v>
+      </c>
+      <c r="E102" s="4">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3">
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="3">
+        <v>37</v>
+      </c>
+      <c r="D103" s="4">
+        <v>84</v>
+      </c>
+      <c r="E103" s="4">
+        <v>3108</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3">
+        <v>103</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C104" s="3">
+        <v>40</v>
+      </c>
+      <c r="D104" s="4">
+        <v>11</v>
+      </c>
+      <c r="E104" s="4">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3">
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="3">
+        <v>43</v>
+      </c>
+      <c r="D105" s="4">
+        <v>18</v>
+      </c>
+      <c r="E105" s="4">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3">
+        <v>105</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="3">
+        <v>46</v>
+      </c>
+      <c r="D106" s="4">
+        <v>25</v>
+      </c>
+      <c r="E106" s="4">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3">
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" s="3">
+        <v>49</v>
+      </c>
+      <c r="D107" s="4">
+        <v>32</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3">
+        <v>107</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C108" s="3">
+        <v>52</v>
+      </c>
+      <c r="D108" s="4">
+        <v>39</v>
+      </c>
+      <c r="E108" s="4">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3">
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="3">
+        <v>55</v>
+      </c>
+      <c r="D109" s="4">
+        <v>46</v>
+      </c>
+      <c r="E109" s="4">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3">
+        <v>109</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110" s="3">
+        <v>58</v>
+      </c>
+      <c r="D110" s="4">
+        <v>53</v>
+      </c>
+      <c r="E110" s="4">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3">
+        <v>110</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C111" s="3">
+        <v>61</v>
+      </c>
+      <c r="D111" s="4">
+        <v>60</v>
+      </c>
+      <c r="E111" s="4">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3">
+        <v>111</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C112" s="3">
+        <v>64</v>
+      </c>
+      <c r="D112" s="4">
+        <v>67</v>
+      </c>
+      <c r="E112" s="4">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3">
+        <v>112</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C113" s="3">
+        <v>67</v>
+      </c>
+      <c r="D113" s="4">
+        <v>74</v>
+      </c>
+      <c r="E113" s="4">
+        <v>4958</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3">
+        <v>113</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C114" s="3">
+        <v>70</v>
+      </c>
+      <c r="D114" s="4">
+        <v>81</v>
+      </c>
+      <c r="E114" s="4">
+        <v>5670</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3">
+        <v>114</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="3">
+        <v>73</v>
+      </c>
+      <c r="D115" s="4">
+        <v>88</v>
+      </c>
+      <c r="E115" s="4">
+        <v>6424</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3">
+        <v>115</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="3">
+        <v>76</v>
+      </c>
+      <c r="D116" s="4">
+        <v>15</v>
+      </c>
+      <c r="E116" s="4">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3">
+        <v>116</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="3">
+        <v>79</v>
+      </c>
+      <c r="D117" s="4">
+        <v>22</v>
+      </c>
+      <c r="E117" s="4">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3">
+        <v>117</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="3">
+        <v>82</v>
+      </c>
+      <c r="D118" s="4">
+        <v>29</v>
+      </c>
+      <c r="E118" s="4">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3">
+        <v>118</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" s="3">
+        <v>85</v>
+      </c>
+      <c r="D119" s="4">
+        <v>36</v>
+      </c>
+      <c r="E119" s="4">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3">
+        <v>119</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" s="3">
+        <v>88</v>
+      </c>
+      <c r="D120" s="4">
+        <v>43</v>
+      </c>
+      <c r="E120" s="4">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3">
+        <v>120</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
+      <c r="D121" s="4">
+        <v>50</v>
+      </c>
+      <c r="E121" s="4">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>